--- a/research/traditional_assets/database/data/new_zealand/new_zealand_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0507</v>
+        <v>0.0609</v>
       </c>
       <c r="F2">
-        <v>0.187</v>
+        <v>0.299</v>
       </c>
       <c r="G2">
-        <v>0.1039016115351993</v>
+        <v>0.09273797841020608</v>
       </c>
       <c r="H2">
-        <v>0.1039016115351993</v>
+        <v>0.09273797841020608</v>
       </c>
       <c r="I2">
-        <v>0.08439355385920271</v>
+        <v>0.07262021589793916</v>
       </c>
       <c r="J2">
-        <v>0.05731907363635189</v>
+        <v>0.0509865012318398</v>
       </c>
       <c r="K2">
-        <v>12.9</v>
+        <v>10.7</v>
       </c>
       <c r="L2">
-        <v>0.05470737913486005</v>
+        <v>0.05250245338567222</v>
       </c>
       <c r="M2">
-        <v>7.29</v>
+        <v>28.7</v>
       </c>
       <c r="N2">
-        <v>0.03459895586141434</v>
+        <v>0.1645642201834862</v>
       </c>
       <c r="O2">
-        <v>0.5651162790697675</v>
+        <v>2.682242990654206</v>
       </c>
       <c r="P2">
-        <v>7.29</v>
+        <v>11.3</v>
       </c>
       <c r="Q2">
-        <v>0.03459895586141434</v>
+        <v>0.06479357798165138</v>
       </c>
       <c r="R2">
-        <v>0.5651162790697675</v>
+        <v>1.05607476635514</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.6062717770034843</v>
       </c>
       <c r="U2">
-        <v>80.3</v>
+        <v>47.9</v>
       </c>
       <c r="V2">
-        <v>0.3811105837683911</v>
+        <v>0.2746559633027523</v>
       </c>
       <c r="W2">
-        <v>0.05740987983978638</v>
+        <v>0.04458333333333333</v>
       </c>
       <c r="X2">
-        <v>0.05089391079886312</v>
+        <v>0.08313709692890811</v>
       </c>
       <c r="Y2">
-        <v>0.006515969040923268</v>
+        <v>-0.03855376359557478</v>
       </c>
       <c r="Z2">
-        <v>1.421766656617425</v>
+        <v>1.166571265025758</v>
       </c>
       <c r="AA2">
-        <v>0.08149434768436403</v>
+        <v>0.05947938724126475</v>
       </c>
       <c r="AB2">
-        <v>0.04698419410281884</v>
+        <v>0.07895829183943168</v>
       </c>
       <c r="AC2">
-        <v>0.03451015358154519</v>
+        <v>-0.01947890459816692</v>
       </c>
       <c r="AD2">
-        <v>27.3</v>
+        <v>19.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>27.3</v>
+        <v>19.9</v>
       </c>
       <c r="AG2">
-        <v>-53</v>
+        <v>-28</v>
       </c>
       <c r="AH2">
-        <v>0.1147058823529412</v>
+        <v>0.1024189397838394</v>
       </c>
       <c r="AI2">
-        <v>0.1014115898959881</v>
+        <v>0.09959959959959959</v>
       </c>
       <c r="AJ2">
-        <v>-0.3360811667723526</v>
+        <v>-0.1912568306010929</v>
       </c>
       <c r="AK2">
-        <v>-0.2805717310746427</v>
+        <v>-0.184331797235023</v>
       </c>
       <c r="AL2">
-        <v>0.261</v>
+        <v>0.508</v>
       </c>
       <c r="AM2">
-        <v>0.261</v>
+        <v>0.508</v>
       </c>
       <c r="AN2">
-        <v>1.114285714285714</v>
+        <v>1.052910052910053</v>
       </c>
       <c r="AO2">
-        <v>76.24521072796934</v>
+        <v>29.13385826771654</v>
       </c>
       <c r="AP2">
-        <v>-2.163265306122449</v>
+        <v>-1.481481481481482</v>
       </c>
       <c r="AQ2">
-        <v>76.24521072796934</v>
+        <v>29.13385826771654</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0507</v>
+        <v>0.0609</v>
       </c>
       <c r="F3">
-        <v>0.187</v>
+        <v>0.299</v>
       </c>
       <c r="G3">
-        <v>0.1039016115351993</v>
+        <v>0.09273797841020608</v>
       </c>
       <c r="H3">
-        <v>0.1039016115351993</v>
+        <v>0.09273797841020608</v>
       </c>
       <c r="I3">
-        <v>0.08439355385920271</v>
+        <v>0.07262021589793916</v>
       </c>
       <c r="J3">
-        <v>0.05731907363635189</v>
+        <v>0.0509865012318398</v>
       </c>
       <c r="K3">
-        <v>12.9</v>
+        <v>10.7</v>
       </c>
       <c r="L3">
-        <v>0.05470737913486005</v>
+        <v>0.05250245338567222</v>
       </c>
       <c r="M3">
-        <v>7.29</v>
+        <v>28.7</v>
       </c>
       <c r="N3">
-        <v>0.03459895586141434</v>
+        <v>0.1645642201834862</v>
       </c>
       <c r="O3">
-        <v>0.5651162790697675</v>
+        <v>2.682242990654206</v>
       </c>
       <c r="P3">
-        <v>7.29</v>
+        <v>11.3</v>
       </c>
       <c r="Q3">
-        <v>0.03459895586141434</v>
+        <v>0.06479357798165138</v>
       </c>
       <c r="R3">
-        <v>0.5651162790697675</v>
+        <v>1.05607476635514</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.6062717770034843</v>
       </c>
       <c r="U3">
-        <v>80.3</v>
+        <v>47.9</v>
       </c>
       <c r="V3">
-        <v>0.3811105837683911</v>
+        <v>0.2746559633027523</v>
       </c>
       <c r="W3">
-        <v>0.05740987983978638</v>
+        <v>0.04458333333333333</v>
       </c>
       <c r="X3">
-        <v>0.05089391079886312</v>
+        <v>0.08313709692890811</v>
       </c>
       <c r="Y3">
-        <v>0.006515969040923268</v>
+        <v>-0.03855376359557478</v>
       </c>
       <c r="Z3">
-        <v>1.421766656617425</v>
+        <v>1.166571265025758</v>
       </c>
       <c r="AA3">
-        <v>0.08149434768436403</v>
+        <v>0.05947938724126475</v>
       </c>
       <c r="AB3">
-        <v>0.04698419410281884</v>
+        <v>0.07895829183943168</v>
       </c>
       <c r="AC3">
-        <v>0.03451015358154519</v>
+        <v>-0.01947890459816692</v>
       </c>
       <c r="AD3">
-        <v>27.3</v>
+        <v>19.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>27.3</v>
+        <v>19.9</v>
       </c>
       <c r="AG3">
-        <v>-53</v>
+        <v>-28</v>
       </c>
       <c r="AH3">
-        <v>0.1147058823529412</v>
+        <v>0.1024189397838394</v>
       </c>
       <c r="AI3">
-        <v>0.1014115898959881</v>
+        <v>0.09959959959959959</v>
       </c>
       <c r="AJ3">
-        <v>-0.3360811667723526</v>
+        <v>-0.1912568306010929</v>
       </c>
       <c r="AK3">
-        <v>-0.2805717310746427</v>
+        <v>-0.184331797235023</v>
       </c>
       <c r="AL3">
-        <v>0.261</v>
+        <v>0.508</v>
       </c>
       <c r="AM3">
-        <v>0.261</v>
+        <v>0.508</v>
       </c>
       <c r="AN3">
-        <v>1.114285714285714</v>
+        <v>1.052910052910053</v>
       </c>
       <c r="AO3">
-        <v>76.24521072796934</v>
+        <v>29.13385826771654</v>
       </c>
       <c r="AP3">
-        <v>-2.163265306122449</v>
+        <v>-1.481481481481482</v>
       </c>
       <c r="AQ3">
-        <v>76.24521072796934</v>
+        <v>29.13385826771654</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0609</v>
+        <v>0.0791</v>
       </c>
       <c r="F2">
-        <v>0.299</v>
+        <v>1.859</v>
       </c>
       <c r="G2">
-        <v>0.09273797841020608</v>
+        <v>0.03695038321903994</v>
       </c>
       <c r="H2">
-        <v>0.09273797841020608</v>
+        <v>0.03695038321903994</v>
       </c>
       <c r="I2">
-        <v>0.07262021589793916</v>
+        <v>0.01799112545381202</v>
       </c>
       <c r="J2">
-        <v>0.0509865012318398</v>
+        <v>0.00899556272690601</v>
       </c>
       <c r="K2">
-        <v>10.7</v>
+        <v>-0.739</v>
       </c>
       <c r="L2">
-        <v>0.05250245338567222</v>
+        <v>-0.002981040742234772</v>
       </c>
       <c r="M2">
-        <v>28.7</v>
+        <v>9.15</v>
       </c>
       <c r="N2">
-        <v>0.1645642201834862</v>
+        <v>0.06241473396998636</v>
       </c>
       <c r="O2">
-        <v>2.682242990654206</v>
+        <v>-12.38159675236806</v>
       </c>
       <c r="P2">
-        <v>11.3</v>
+        <v>9.15</v>
       </c>
       <c r="Q2">
-        <v>0.06479357798165138</v>
+        <v>0.06241473396998636</v>
       </c>
       <c r="R2">
-        <v>1.05607476635514</v>
+        <v>-12.38159675236806</v>
       </c>
       <c r="S2">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.6062717770034843</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>47.9</v>
+        <v>33.1</v>
       </c>
       <c r="V2">
-        <v>0.2746559633027523</v>
+        <v>0.2257844474761255</v>
       </c>
       <c r="W2">
-        <v>0.04458333333333333</v>
+        <v>-0.004107837687604224</v>
       </c>
       <c r="X2">
-        <v>0.08313709692890811</v>
+        <v>0.0720992535226132</v>
       </c>
       <c r="Y2">
-        <v>-0.03855376359557478</v>
+        <v>-0.07620709121021743</v>
       </c>
       <c r="Z2">
-        <v>1.166571265025758</v>
+        <v>1.748236953455571</v>
       </c>
       <c r="AA2">
-        <v>0.05947938724126475</v>
+        <v>0.01572637517630465</v>
       </c>
       <c r="AB2">
-        <v>0.07895829183943168</v>
+        <v>0.06742116355243741</v>
       </c>
       <c r="AC2">
-        <v>-0.01947890459816692</v>
+        <v>-0.05169478837613276</v>
       </c>
       <c r="AD2">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="AG2">
-        <v>-28</v>
+        <v>-13.5</v>
       </c>
       <c r="AH2">
-        <v>0.1024189397838394</v>
+        <v>0.1179302045728039</v>
       </c>
       <c r="AI2">
-        <v>0.09959959959959959</v>
+        <v>0.09790209790209792</v>
       </c>
       <c r="AJ2">
-        <v>-0.1912568306010929</v>
+        <v>-0.101427498121713</v>
       </c>
       <c r="AK2">
-        <v>-0.184331797235023</v>
+        <v>-0.08078994614003591</v>
       </c>
       <c r="AL2">
-        <v>0.508</v>
+        <v>0.732</v>
       </c>
       <c r="AM2">
-        <v>0.508</v>
+        <v>0.732</v>
       </c>
       <c r="AN2">
-        <v>1.052910052910053</v>
+        <v>2.139737991266376</v>
       </c>
       <c r="AO2">
-        <v>29.13385826771654</v>
+        <v>6.092896174863388</v>
       </c>
       <c r="AP2">
-        <v>-1.481481481481482</v>
+        <v>-1.473799126637555</v>
       </c>
       <c r="AQ2">
-        <v>29.13385826771654</v>
+        <v>6.092896174863388</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0609</v>
+        <v>0.0791</v>
       </c>
       <c r="F3">
-        <v>0.299</v>
+        <v>1.859</v>
       </c>
       <c r="G3">
-        <v>0.09273797841020608</v>
+        <v>0.03695038321903994</v>
       </c>
       <c r="H3">
-        <v>0.09273797841020608</v>
+        <v>0.03695038321903994</v>
       </c>
       <c r="I3">
-        <v>0.07262021589793916</v>
+        <v>0.01799112545381202</v>
       </c>
       <c r="J3">
-        <v>0.0509865012318398</v>
+        <v>0.00899556272690601</v>
       </c>
       <c r="K3">
-        <v>10.7</v>
+        <v>-0.739</v>
       </c>
       <c r="L3">
-        <v>0.05250245338567222</v>
+        <v>-0.002981040742234772</v>
       </c>
       <c r="M3">
-        <v>28.7</v>
+        <v>9.15</v>
       </c>
       <c r="N3">
-        <v>0.1645642201834862</v>
+        <v>0.06241473396998636</v>
       </c>
       <c r="O3">
-        <v>2.682242990654206</v>
+        <v>-12.38159675236806</v>
       </c>
       <c r="P3">
-        <v>11.3</v>
+        <v>9.15</v>
       </c>
       <c r="Q3">
-        <v>0.06479357798165138</v>
+        <v>0.06241473396998636</v>
       </c>
       <c r="R3">
-        <v>1.05607476635514</v>
+        <v>-12.38159675236806</v>
       </c>
       <c r="S3">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.6062717770034843</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>47.9</v>
+        <v>33.1</v>
       </c>
       <c r="V3">
-        <v>0.2746559633027523</v>
+        <v>0.2257844474761255</v>
       </c>
       <c r="W3">
-        <v>0.04458333333333333</v>
+        <v>-0.004107837687604224</v>
       </c>
       <c r="X3">
-        <v>0.08313709692890811</v>
+        <v>0.0720992535226132</v>
       </c>
       <c r="Y3">
-        <v>-0.03855376359557478</v>
+        <v>-0.07620709121021743</v>
       </c>
       <c r="Z3">
-        <v>1.166571265025758</v>
+        <v>1.748236953455571</v>
       </c>
       <c r="AA3">
-        <v>0.05947938724126475</v>
+        <v>0.01572637517630465</v>
       </c>
       <c r="AB3">
-        <v>0.07895829183943168</v>
+        <v>0.06742116355243741</v>
       </c>
       <c r="AC3">
-        <v>-0.01947890459816692</v>
+        <v>-0.05169478837613276</v>
       </c>
       <c r="AD3">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="AG3">
-        <v>-28</v>
+        <v>-13.5</v>
       </c>
       <c r="AH3">
-        <v>0.1024189397838394</v>
+        <v>0.1179302045728039</v>
       </c>
       <c r="AI3">
-        <v>0.09959959959959959</v>
+        <v>0.09790209790209792</v>
       </c>
       <c r="AJ3">
-        <v>-0.1912568306010929</v>
+        <v>-0.101427498121713</v>
       </c>
       <c r="AK3">
-        <v>-0.184331797235023</v>
+        <v>-0.08078994614003591</v>
       </c>
       <c r="AL3">
-        <v>0.508</v>
+        <v>0.732</v>
       </c>
       <c r="AM3">
-        <v>0.508</v>
+        <v>0.732</v>
       </c>
       <c r="AN3">
-        <v>1.052910052910053</v>
+        <v>2.139737991266376</v>
       </c>
       <c r="AO3">
-        <v>29.13385826771654</v>
+        <v>6.092896174863388</v>
       </c>
       <c r="AP3">
-        <v>-1.481481481481482</v>
+        <v>-1.473799126637555</v>
       </c>
       <c r="AQ3">
-        <v>29.13385826771654</v>
+        <v>6.092896174863388</v>
       </c>
     </row>
   </sheetData>
